--- a/load-tests/reports/Load_Test_Report.xlsx
+++ b/load-tests/reports/Load_Test_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 10:22:30 am</t>
+    <t>28/7/2026, 11:37:02 am</t>
   </si>
   <si>
     <t>Target API Endpoint</t>

--- a/load-tests/reports/Load_Test_Report.xlsx
+++ b/load-tests/reports/Load_Test_Report.xlsx
@@ -24,7 +24,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>28/7/2026, 11:37:02 am</t>
+    <t>28/7/2026, 11:51:24 am</t>
   </si>
   <si>
     <t>Target API Endpoint</t>
